--- a/Employee_Reports_wi48/Michael Jorge Toscano Masaoy Q0616.xlsx
+++ b/Employee_Reports_wi48/Michael Jorge Toscano Masaoy Q0616.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1001,20 +1001,20 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>11-Jul-2028</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>469</v>
+        <v>726</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Cool Room (Cargo Trainings)</t>
+          <t>Truck dock 20FT (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-011</t>
+          <t>LSME-CRG-M-020</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>11-Jul-2028</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>469</v>
+        <v>726</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Climate Control Center (Cargo Trainings)</t>
+          <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-014</t>
+          <t>LSME-CRG-M-011</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1128,40 +1128,40 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Lodige LOTO Procedure (SOPs)</t>
+          <t>Climate Control Center (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ELECTRICAL SAFETY</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>LSME-OHS-SOP-021</t>
+          <t>LSME-CRG-M-014</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>20-Oct-2025</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
+          <t>25-Oct-2027</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>99</v>
+        <v>466</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1177,18 +1177,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Equipment Operation Procedure
-(SOP-031) (SOPs)</t>
+          <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-031</t>
+          <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1198,20 +1197,20 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>04-Dec-2025</t>
+          <t>20-Oct-2025</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>04-Dec-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1227,7 +1226,8 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+          <t>Equipment Operation Procedure
+(SOP-031) (SOPs)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-028</t>
+          <t>LSME-CRG-SOP-031</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1276,28 +1276,40 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
+          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-028</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>04-Dec-2025</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>04-Dec-2026</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1313,7 +1325,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1330,11 +1342,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1350,48 +1362,85 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>25-Oct-2025</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>25-Oct-2026</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>Matar LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>MATAR</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>FM-DE-24-SOP-SA-013</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>04-Dec-2025</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>04-Dec-2026</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1810,7 +1859,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1905,7 +1954,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1934,7 +1983,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1963,7 +2012,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1992,7 +2041,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2021,7 +2070,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7960</v>
+        <v>7957</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2050,7 +2099,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7936</v>
+        <v>7933</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2079,7 +2128,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2108,7 +2157,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2137,7 +2186,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2166,7 +2215,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2195,7 +2244,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2224,7 +2273,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2253,7 +2302,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2282,7 +2331,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7971</v>
+        <v>7968</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2311,7 +2360,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7972</v>
+        <v>7969</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2340,7 +2389,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2369,7 +2418,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7967</v>
+        <v>7964</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2398,7 +2447,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7972</v>
+        <v>7969</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
